--- a/output/pdf_financials_xlsx/STUV.xlsx
+++ b/output/pdf_financials_xlsx/STUV.xlsx
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.16832</v>
+        <v>-0.16832</v>
       </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.16832</v>
+        <v>-0.16832</v>
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.16832</v>
+        <v>-0.16832</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>-0.16832</v>
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.16832</v>
+        <v>-0.16832</v>
       </c>
       <c r="C27" s="1" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.16832</v>
+        <v>-0.16832</v>
       </c>
       <c r="C29" s="1" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="1" t="inlineStr">
         <is>
@@ -4694,22 +4694,22 @@
         <v>0</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-0.807675</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-0.122927</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-0.225237</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-0.11903</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>-0.123149</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>-0.168784</v>
       </c>
     </row>
     <row r="119">
@@ -9583,7 +9583,11 @@
           <t>Exploration and evaluation expenditures 4</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
@@ -12099,7 +12103,11 @@
           <t>Exploration and evaluation expenditures 5</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
           <t>-</t>
@@ -18362,7 +18370,7 @@
         </is>
       </c>
       <c r="E217" s="5" t="n">
-        <v>0.16832</v>
+        <v>-0.16832</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/STUV.xlsx
+++ b/output/pdf_financials_xlsx/STUV.xlsx
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.585815</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0.537346</v>
@@ -1665,16 +1665,16 @@
         <v>0.032026</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.018632</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.062982</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.251583</v>
       </c>
     </row>
     <row r="35">
@@ -1725,7 +1725,7 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.585815</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>0.537346</v>
@@ -1737,16 +1737,16 @@
         <v>0.032026</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.018632</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.062982</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.251583</v>
       </c>
     </row>
     <row r="37">
@@ -2169,16 +2169,16 @@
         <v>0.001287</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.020277</v>
+        <v>0.001645</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.06468500000000001</v>
+        <v>0.001703</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.251583</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -7905,7 +7905,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -13483,7 +13483,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">

--- a/output/pdf_financials_xlsx/STUV.xlsx
+++ b/output/pdf_financials_xlsx/STUV.xlsx
@@ -3998,10 +3998,8 @@
           <t xml:space="preserve">  Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B99" s="3" t="n">
+        <v>-0.16832</v>
       </c>
       <c r="C99" s="3" t="n">
         <v>-0.16832</v>
@@ -4034,10 +4032,8 @@
           <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B100" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C100" s="3" t="n">
         <v>0</v>
@@ -4070,10 +4066,8 @@
           <t xml:space="preserve">    Change In Receivables</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B101" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C101" s="3" t="n">
         <v>0</v>
@@ -4106,10 +4100,8 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B102" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C102" s="3" t="n">
         <v>0</v>
@@ -4142,10 +4134,8 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B103" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C103" s="3" t="n">
         <v>0</v>
@@ -4178,10 +4168,8 @@
           <t xml:space="preserve">    Change In Payables And Accrued Expense</t>
         </is>
       </c>
-      <c r="B104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B104" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C104" s="3" t="n">
         <v>0</v>
@@ -4214,10 +4202,8 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B105" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C105" s="3" t="n">
         <v>0</v>
@@ -4250,10 +4236,8 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B106" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C106" s="3" t="n">
         <v>0</v>
@@ -4286,10 +4270,8 @@
           <t xml:space="preserve">  Stock Based Compensation</t>
         </is>
       </c>
-      <c r="B107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B107" s="3" t="n">
+        <v>0.09780999999999999</v>
       </c>
       <c r="C107" s="3" t="n">
         <v>0.09780999999999999</v>
@@ -4322,10 +4304,8 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C108" s="3" t="n">
         <v>0</v>
@@ -4358,10 +4338,8 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B109" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C109" s="3" t="n">
         <v>0</v>
@@ -4394,10 +4372,8 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B110" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C110" s="3" t="n">
         <v>0</v>
@@ -4415,13 +4391,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>0</v>
+        <v>0.027017</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>0.033008</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>0</v>
+        <v>0.004071</v>
       </c>
     </row>
     <row r="111">
@@ -4430,10 +4406,8 @@
           <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B111" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
         <v>0</v>
@@ -4466,10 +4440,8 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B112" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C112" s="3" t="n">
         <v>0</v>
@@ -4502,10 +4474,8 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B113" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C113" s="3" t="n">
         <v>0</v>
@@ -4538,10 +4508,8 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B114" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C114" s="3" t="n">
         <v>0</v>
@@ -4574,10 +4542,8 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C115" s="3" t="n">
         <v>0</v>
@@ -4610,10 +4576,8 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B116" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C116" s="3" t="n">
         <v>0</v>
@@ -4646,10 +4610,8 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C117" s="3" t="n">
         <v>0</v>
@@ -4682,10 +4644,8 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B118" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C118" s="3" t="n">
         <v>0</v>
@@ -4718,10 +4678,8 @@
           <t>Cash Flow from Investing</t>
         </is>
       </c>
-      <c r="B119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B119" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C119" s="3" t="n">
         <v>0</v>
@@ -4756,10 +4714,8 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B120" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C120" s="3" t="n">
         <v>0</v>
@@ -4792,10 +4748,8 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B121" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C121" s="3" t="n">
         <v>0</v>
@@ -4828,10 +4782,8 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B122" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C122" s="3" t="n">
         <v>0</v>
@@ -4864,10 +4816,8 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C123" s="3" t="n">
         <v>0</v>
@@ -4900,10 +4850,8 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B124" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C124" s="3" t="n">
         <v>0</v>
@@ -4936,10 +4884,8 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B125" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C125" s="3" t="n">
         <v>0</v>
@@ -4972,10 +4918,8 @@
           <t xml:space="preserve">  Cash Flow for Dividends</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B126" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C126" s="3" t="n">
         <v>0</v>
@@ -5060,10 +5004,8 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B128" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C128" s="3" t="n">
         <v>0</v>
@@ -5096,10 +5038,8 @@
           <t>Cash Flow from Financing</t>
         </is>
       </c>
-      <c r="B129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B129" s="3" t="n">
+        <v>0.649382</v>
       </c>
       <c r="C129" s="3" t="n">
         <v>0.649382</v>
@@ -5134,10 +5074,8 @@
           <t xml:space="preserve">  Beginning Cash Position</t>
         </is>
       </c>
-      <c r="B130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B130" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C130" s="3" t="n">
         <v>0</v>
@@ -5172,10 +5110,8 @@
           <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C131" s="3" t="n">
         <v>0</v>
@@ -5208,10 +5144,8 @@
           <t xml:space="preserve">  Net Change in Cash</t>
         </is>
       </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B132" s="3" t="n">
+        <v>0.585815</v>
       </c>
       <c r="C132" s="3" t="n">
         <v>0.585815</v>
@@ -5244,10 +5178,8 @@
           <t>Ending Cash Position</t>
         </is>
       </c>
-      <c r="B133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B133" s="3" t="n">
+        <v>0.585815</v>
       </c>
       <c r="C133" s="3" t="n">
         <v>0.585815</v>
@@ -5282,10 +5214,8 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B134" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
         <v>0</v>
@@ -5318,10 +5248,8 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B135" s="3" t="n">
+        <v>-0.063567</v>
       </c>
       <c r="C135" s="3" t="n">
         <v>-0.063567</v>
@@ -5359,7 +5287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M238"/>
+  <dimension ref="A1:M241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8934,7 +8862,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -9237,7 +9169,11 @@
           <t>Accretion 7,8</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>-</t>
@@ -9881,10 +9817,8 @@
           <t>FinancingCashFlow</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E77" s="5" t="n">
+        <v>0.649382</v>
       </c>
       <c r="F77" s="5" t="n">
         <v>0.649382</v>
@@ -10182,10 +10116,8 @@
           <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E82" s="5" t="n">
+        <v>-0.16832</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10474,7 +10406,11 @@
           <t>Accretion 7</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>-</t>
@@ -12797,10 +12733,8 @@
           <t>StockBasedCompensation</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E125" s="5" t="n">
+        <v>0.09780999999999999</v>
       </c>
       <c r="F125" s="5" t="n">
         <v>0.09780999999999999</v>
@@ -12858,10 +12792,8 @@
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E126" s="5" t="n">
+        <v>0.006943</v>
       </c>
       <c r="F126" s="5" t="n">
         <v>0.006943</v>
@@ -12921,10 +12853,8 @@
           <t>OperatingCashFlow</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E127" s="5" t="n">
+        <v>-0.063567</v>
       </c>
       <c r="F127" s="5" t="n">
         <v>-0.063567</v>
@@ -12984,10 +12914,8 @@
           <t>CommonStockIssuance</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E128" s="5" t="n">
+        <v>0.649382</v>
       </c>
       <c r="F128" s="5" t="n">
         <v>0.649382</v>
@@ -13159,28 +13087,26 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>General and administrative 10 $</t>
+          <t>Increase in cash</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E131" s="5" t="n">
+        <v>0.585815</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13212,30 +13138,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L131" s="5" t="n">
-        <v>0.022044</v>
-      </c>
-      <c r="M131" s="5" t="n">
-        <v>0.058486</v>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Finance expense 6,7</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr"/>
+          <t>Cash, beginning of period</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
           <t>-</t>
@@ -13271,38 +13205,40 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L132" s="5" t="n">
-        <v>0.07850799999999999</v>
-      </c>
-      <c r="M132" s="5" t="n">
-        <v>0.049184</v>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Cash, end of period $</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E133" s="5" t="n">
+        <v>0.585815</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13339,8 +13275,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M133" s="5" t="n">
-        <v>0.019196</v>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="134">
@@ -13356,12 +13294,12 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Loss (gain) on foreign exchange</t>
+          <t>General and administrative 10 $</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>ForeignExchangeTradingGains</t>
+          <t>GeneralAndAdministrativeExpense</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -13400,10 +13338,10 @@
         </is>
       </c>
       <c r="L134" s="5" t="n">
-        <v>-0.000233</v>
+        <v>0.022044</v>
       </c>
       <c r="M134" s="5" t="n">
-        <v>0.000281</v>
+        <v>0.058486</v>
       </c>
     </row>
     <row r="135">
@@ -13419,7 +13357,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Impairment of property 4</t>
+          <t>Finance expense 6,7</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
@@ -13453,16 +13391,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K135" s="5" t="n">
-        <v>0.438393</v>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L135" s="5" t="n">
-        <v>0.222307</v>
-      </c>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.07850799999999999</v>
+      </c>
+      <c r="M135" s="5" t="n">
+        <v>0.049184</v>
       </c>
     </row>
     <row r="136">
@@ -13478,7 +13416,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Total expenses</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -13521,11 +13459,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L136" s="5" t="n">
-        <v>0.322626</v>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M136" s="5" t="n">
-        <v>0.127147</v>
+        <v>0.019196</v>
       </c>
     </row>
     <row r="137">
@@ -13536,15 +13476,19 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Other item</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Gain on settlement of trade and other payables 11</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr"/>
+          <t>Loss (gain) on foreign exchange</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>ForeignExchangeTradingGains</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>
@@ -13580,13 +13524,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L137" s="5" t="n">
+        <v>-0.000233</v>
       </c>
       <c r="M137" s="5" t="n">
-        <v>-0.246571</v>
+        <v>0.000281</v>
       </c>
     </row>
     <row r="138">
@@ -13597,19 +13539,15 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Other item</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Net income (loss)</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Impairment of property 4</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
           <t>-</t>
@@ -13640,16 +13578,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K138" s="5" t="n">
+        <v>0.438393</v>
       </c>
       <c r="L138" s="5" t="n">
-        <v>-0.322626</v>
-      </c>
-      <c r="M138" s="5" t="n">
-        <v>0.119424</v>
+        <v>0.222307</v>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="139">
@@ -13660,15 +13598,19 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Other comprehensive loss</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Foreign exchange translation adjustment</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr"/>
+          <t>Total expenses</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
           <t>-</t>
@@ -13705,10 +13647,10 @@
         </is>
       </c>
       <c r="L139" s="5" t="n">
-        <v>-0.035155</v>
+        <v>0.322626</v>
       </c>
       <c r="M139" s="5" t="n">
-        <v>0.032457</v>
+        <v>0.127147</v>
       </c>
     </row>
     <row r="140">
@@ -13719,19 +13661,15 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Other comprehensive loss</t>
+          <t>Other item</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Net income (loss) and comprehensive income (loss) $</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Gain on settlement of trade and other payables 11</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr">
         <is>
           <t>-</t>
@@ -13767,11 +13705,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L140" s="5" t="n">
-        <v>-0.357781</v>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M140" s="5" t="n">
-        <v>0.151881</v>
+        <v>-0.246571</v>
       </c>
     </row>
     <row r="141">
@@ -13782,15 +13722,19 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Net income (loss) per share</t>
+          <t>Other item</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Basic 9(d) $</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr"/>
+          <t>Net income (loss)</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E141" t="inlineStr">
         <is>
           <t>-</t>
@@ -13827,10 +13771,10 @@
         </is>
       </c>
       <c r="L141" s="5" t="n">
-        <v>-3e-08</v>
+        <v>-0.322626</v>
       </c>
       <c r="M141" s="5" t="n">
-        <v>1e-08</v>
+        <v>0.119424</v>
       </c>
     </row>
     <row r="142">
@@ -13841,12 +13785,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Net income (loss) per share</t>
+          <t>Other comprehensive loss</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Diluted</t>
+          <t>Foreign exchange translation adjustment</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
@@ -13886,10 +13830,10 @@
         </is>
       </c>
       <c r="L142" s="5" t="n">
-        <v>-3e-08</v>
+        <v>-0.035155</v>
       </c>
       <c r="M142" s="5" t="n">
-        <v>1e-08</v>
+        <v>0.032457</v>
       </c>
     </row>
     <row r="143">
@@ -13900,15 +13844,19 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Weighted average common shares</t>
+          <t>Other comprehensive loss</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Basic 9(d)</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr"/>
+          <t>Net income (loss) and comprehensive income (loss) $</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
           <t>-</t>
@@ -13945,10 +13893,10 @@
         </is>
       </c>
       <c r="L143" s="5" t="n">
-        <v>9.882826</v>
+        <v>-0.357781</v>
       </c>
       <c r="M143" s="5" t="n">
-        <v>9.882826</v>
+        <v>0.151881</v>
       </c>
     </row>
     <row r="144">
@@ -13959,12 +13907,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Weighted average common shares</t>
+          <t>Net income (loss) per share</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Diluted</t>
+          <t>Basic 9(d) $</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
@@ -14004,10 +13952,10 @@
         </is>
       </c>
       <c r="L144" s="5" t="n">
-        <v>9.882826</v>
+        <v>-3e-08</v>
       </c>
       <c r="M144" s="5" t="n">
-        <v>11.308647</v>
+        <v>1e-08</v>
       </c>
     </row>
     <row r="145">
@@ -14018,12 +13966,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Notes        Share Capital         Surplus            Loss          Deficit          Equity</t>
+          <t>Net income (loss) per share</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2023 $ 4,725,998 $ 677,302 $ (48,268) $</t>
+          <t>Diluted</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
@@ -14063,10 +14011,10 @@
         </is>
       </c>
       <c r="L145" s="5" t="n">
-        <v>3.408484</v>
+        <v>-3e-08</v>
       </c>
       <c r="M145" s="5" t="n">
-        <v>-1.946548</v>
+        <v>1e-08</v>
       </c>
     </row>
     <row r="146">
@@ -14077,12 +14025,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Notes        Share Capital         Surplus            Loss          Deficit          Equity</t>
+          <t>Weighted average common shares</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss – – (35,155)</t>
+          <t>Basic 9(d)</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
@@ -14122,10 +14070,10 @@
         </is>
       </c>
       <c r="L146" s="5" t="n">
-        <v>-0.357781</v>
+        <v>9.882826</v>
       </c>
       <c r="M146" s="5" t="n">
-        <v>-0.322626</v>
+        <v>9.882826</v>
       </c>
     </row>
     <row r="147">
@@ -14136,12 +14084,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Notes        Share Capital         Surplus            Loss          Deficit          Equity</t>
+          <t>Weighted average common shares</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2024 $ 4,725,998 $ 677,302 $ (83,423) $</t>
+          <t>Diluted</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
@@ -14181,10 +14129,10 @@
         </is>
       </c>
       <c r="L147" s="5" t="n">
-        <v>3.050703</v>
+        <v>9.882826</v>
       </c>
       <c r="M147" s="5" t="n">
-        <v>-2.269174</v>
+        <v>11.308647</v>
       </c>
     </row>
     <row r="148">
@@ -14200,7 +14148,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Equity portion of term loan 8 – 112,305 –</t>
+          <t>Balance, December 31, 2023 $ 4,725,998 $ 677,302 $ (48,268) $</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
@@ -14240,12 +14188,10 @@
         </is>
       </c>
       <c r="L148" s="5" t="n">
-        <v>0.112305</v>
-      </c>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.408484</v>
+      </c>
+      <c r="M148" s="5" t="n">
+        <v>-1.946548</v>
       </c>
     </row>
     <row r="149">
@@ -14261,14 +14207,10 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Net income and comprehensive income – – 32,457</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Net loss and comprehensive loss – – (35,155)</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
           <t>-</t>
@@ -14305,10 +14247,10 @@
         </is>
       </c>
       <c r="L149" s="5" t="n">
-        <v>0.151881</v>
+        <v>-0.357781</v>
       </c>
       <c r="M149" s="5" t="n">
-        <v>0.119424</v>
+        <v>-0.322626</v>
       </c>
     </row>
     <row r="150">
@@ -14324,7 +14266,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2025 $ 4,725,998 $ 789,607 $ (50,966) $</t>
+          <t>Balance, December 31, 2024 $ 4,725,998 $ 677,302 $ (83,423) $</t>
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
@@ -14364,10 +14306,10 @@
         </is>
       </c>
       <c r="L150" s="5" t="n">
-        <v>3.314889</v>
+        <v>3.050703</v>
       </c>
       <c r="M150" s="5" t="n">
-        <v>-2.14975</v>
+        <v>-2.269174</v>
       </c>
     </row>
     <row r="151">
@@ -14378,19 +14320,15 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Notes        Share Capital         Surplus            Loss          Deficit          Equity</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>General and administrative 9 $</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Equity portion of term loan 8 – 112,305 –</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
           <t>-</t>
@@ -14416,14 +14354,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J151" s="5" t="n">
-        <v>0.237332</v>
-      </c>
-      <c r="K151" s="5" t="n">
-        <v>0.118225</v>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L151" s="5" t="n">
-        <v>0.022044</v>
+        <v>0.112305</v>
       </c>
       <c r="M151" t="inlineStr">
         <is>
@@ -14439,15 +14381,19 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Notes        Share Capital         Surplus            Loss          Deficit          Equity</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Stock-based compensation</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr"/>
+          <t>Net income and comprehensive income – – 32,457</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
           <t>-</t>
@@ -14478,18 +14424,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K152" s="5" t="n">
-        <v>0.005183</v>
-      </c>
-      <c r="L152" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L152" s="5" t="n">
+        <v>0.151881</v>
+      </c>
+      <c r="M152" s="5" t="n">
+        <v>0.119424</v>
       </c>
     </row>
     <row r="153">
@@ -14500,12 +14444,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Notes        Share Capital         Surplus            Loss          Deficit          Equity</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Convertible Debenture interest 7</t>
+          <t>Balance, December 31, 2025 $ 4,725,998 $ 789,607 $ (50,966) $</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
@@ -14539,16 +14483,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K153" s="5" t="n">
-        <v>0.041708</v>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L153" s="5" t="n">
-        <v>0.0455</v>
-      </c>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.314889</v>
+      </c>
+      <c r="M153" s="5" t="n">
+        <v>-2.14975</v>
       </c>
     </row>
     <row r="154">
@@ -14564,10 +14508,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Convertible Debenture accretion 7</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr"/>
+          <t>General and administrative 9 $</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E154" t="inlineStr">
         <is>
           <t>-</t>
@@ -14593,16 +14541,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J154" s="5" t="n">
+        <v>0.237332</v>
       </c>
       <c r="K154" s="5" t="n">
-        <v>0.027017</v>
+        <v>0.118225</v>
       </c>
       <c r="L154" s="5" t="n">
-        <v>0.033008</v>
+        <v>0.022044</v>
       </c>
       <c r="M154" t="inlineStr">
         <is>
@@ -14623,14 +14569,10 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Unrealized gain on foreign exchange</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>ForeignExchangeTradingGains</t>
-        </is>
-      </c>
+          <t>Stock-based compensation</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
           <t>-</t>
@@ -14656,16 +14598,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J155" s="5" t="n">
-        <v>-0.040913</v>
-      </c>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L155" s="5" t="n">
-        <v>-0.000233</v>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K155" s="5" t="n">
+        <v>0.005183</v>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
@@ -14686,14 +14630,10 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Expenses total</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Convertible Debenture interest 7</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">
         <is>
           <t>-</t>
@@ -14704,23 +14644,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G156" s="5" t="n">
-        <v>0.057333</v>
-      </c>
-      <c r="H156" s="5" t="n">
-        <v>0.634971</v>
-      </c>
-      <c r="I156" s="5" t="n">
-        <v>0.401039</v>
-      </c>
-      <c r="J156" s="5" t="n">
-        <v>0.250369</v>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K156" s="5" t="n">
-        <v>0.630526</v>
+        <v>0.041708</v>
       </c>
       <c r="L156" s="5" t="n">
-        <v>0.322626</v>
+        <v>0.0455</v>
       </c>
       <c r="M156" t="inlineStr">
         <is>
@@ -14741,14 +14689,10 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Net loss</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Convertible Debenture accretion 7</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
           <t>-</t>
@@ -14769,17 +14713,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I157" s="5" t="n">
-        <v>-0.401039</v>
-      </c>
-      <c r="J157" s="5" t="n">
-        <v>-0.250369</v>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K157" s="5" t="n">
-        <v>-0.630526</v>
+        <v>0.027017</v>
       </c>
       <c r="L157" s="5" t="n">
-        <v>-0.322626</v>
+        <v>0.033008</v>
       </c>
       <c r="M157" t="inlineStr">
         <is>
@@ -14795,15 +14743,19 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Other comprehensive income</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Foreign exchange translation adjustment 3(i)</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr"/>
+          <t>Unrealized gain on foreign exchange</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>ForeignExchangeTradingGains</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
           <t>-</t>
@@ -14829,16 +14781,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K158" s="5" t="n">
-        <v>-0.051183</v>
+      <c r="J158" s="5" t="n">
+        <v>-0.040913</v>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L158" s="5" t="n">
-        <v>-0.035155</v>
+        <v>-0.000233</v>
       </c>
       <c r="M158" t="inlineStr">
         <is>
@@ -14854,17 +14806,17 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Other comprehensive income</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss $</t>
+          <t>Expenses total</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -14877,25 +14829,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G159" s="5" t="n">
+        <v>0.057333</v>
       </c>
       <c r="H159" s="5" t="n">
-        <v>-0.438961</v>
+        <v>0.634971</v>
       </c>
       <c r="I159" s="5" t="n">
-        <v>-0.398105</v>
+        <v>0.401039</v>
       </c>
       <c r="J159" s="5" t="n">
-        <v>-0.250388</v>
+        <v>0.250369</v>
       </c>
       <c r="K159" s="5" t="n">
-        <v>-0.681709</v>
+        <v>0.630526</v>
       </c>
       <c r="L159" s="5" t="n">
-        <v>-0.357781</v>
+        <v>0.322626</v>
       </c>
       <c r="M159" t="inlineStr">
         <is>
@@ -14911,17 +14861,17 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Net loss per share</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Basic and diluted $</t>
+          <t>Net loss</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -14934,23 +14884,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G160" s="5" t="n">
-        <v>-9e-08</v>
-      </c>
-      <c r="H160" s="5" t="n">
-        <v>-5.999999999999999e-08</v>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I160" s="5" t="n">
-        <v>-1e-08</v>
+        <v>-0.401039</v>
       </c>
       <c r="J160" s="5" t="n">
-        <v>-1e-08</v>
+        <v>-0.250369</v>
       </c>
       <c r="K160" s="5" t="n">
-        <v>-2e-08</v>
+        <v>-0.630526</v>
       </c>
       <c r="L160" s="5" t="n">
-        <v>-1e-08</v>
+        <v>-0.322626</v>
       </c>
       <c r="M160" t="inlineStr">
         <is>
@@ -14966,12 +14920,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Weighted average common shares:                         8</t>
+          <t>Other comprehensive income</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Basic and diluted</t>
+          <t>Foreign exchange translation adjustment 3(i)</t>
         </is>
       </c>
       <c r="D161" t="inlineStr"/>
@@ -15000,14 +14954,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J161" s="5" t="n">
-        <v>29.648484</v>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K161" s="5" t="n">
-        <v>29.648484</v>
+        <v>-0.051183</v>
       </c>
       <c r="L161" s="5" t="n">
-        <v>29.648484</v>
+        <v>-0.035155</v>
       </c>
       <c r="M161" t="inlineStr">
         <is>
@@ -15023,15 +14979,19 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Notes     Share Capital           Surplus            OCI             Deficit           Equity</t>
+          <t>Other comprehensive income</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>As at December 31, 2022 $ 4,725,998 $ 612,094 $ 2,915 $</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr"/>
+          <t>Net loss and comprehensive loss $</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
           <t>-</t>
@@ -15047,26 +15007,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H162" s="5" t="n">
+        <v>-0.438961</v>
+      </c>
+      <c r="I162" s="5" t="n">
+        <v>-0.398105</v>
+      </c>
+      <c r="J162" s="5" t="n">
+        <v>-0.250388</v>
       </c>
       <c r="K162" s="5" t="n">
-        <v>4.024985</v>
+        <v>-0.681709</v>
       </c>
       <c r="L162" s="5" t="n">
-        <v>-1.316022</v>
+        <v>-0.357781</v>
       </c>
       <c r="M162" t="inlineStr">
         <is>
@@ -15082,15 +15036,19 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Notes     Share Capital           Surplus            OCI             Deficit           Equity</t>
+          <t>Net loss per share</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Share-based compensation - 5,183 -</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr"/>
+          <t>Basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E163" t="inlineStr">
         <is>
           <t>-</t>
@@ -15101,33 +15059,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G163" s="5" t="n">
+        <v>-9e-08</v>
+      </c>
+      <c r="H163" s="5" t="n">
+        <v>-5.999999999999999e-08</v>
+      </c>
+      <c r="I163" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="J163" s="5" t="n">
+        <v>-1e-08</v>
       </c>
       <c r="K163" s="5" t="n">
-        <v>0.005183</v>
-      </c>
-      <c r="L163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2e-08</v>
+      </c>
+      <c r="L163" s="5" t="n">
+        <v>-1e-08</v>
       </c>
       <c r="M163" t="inlineStr">
         <is>
@@ -15143,12 +15091,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Notes     Share Capital           Surplus            OCI             Deficit           Equity</t>
+          <t>Weighted average common shares:                         8</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Equity portion of Convertible Debentures 7 - 60,025 -</t>
+          <t>Basic and diluted</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -15177,18 +15125,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J164" s="5" t="n">
+        <v>29.648484</v>
       </c>
       <c r="K164" s="5" t="n">
-        <v>0.060025</v>
-      </c>
-      <c r="L164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>29.648484</v>
+      </c>
+      <c r="L164" s="5" t="n">
+        <v>29.648484</v>
       </c>
       <c r="M164" t="inlineStr">
         <is>
@@ -15209,7 +15153,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Net and comprehensive loss - - (51,183)</t>
+          <t>As at December 31, 2022 $ 4,725,998 $ 612,094 $ 2,915 $</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
@@ -15244,10 +15188,10 @@
         </is>
       </c>
       <c r="K165" s="5" t="n">
-        <v>-0.681709</v>
+        <v>4.024985</v>
       </c>
       <c r="L165" s="5" t="n">
-        <v>-0.630526</v>
+        <v>-1.316022</v>
       </c>
       <c r="M165" t="inlineStr">
         <is>
@@ -15268,7 +15212,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Balance December 31, 2023 $ 4,725,998 $ 677,302 $ (48,268) $</t>
+          <t>Share-based compensation - 5,183 -</t>
         </is>
       </c>
       <c r="D166" t="inlineStr"/>
@@ -15303,10 +15247,12 @@
         </is>
       </c>
       <c r="K166" s="5" t="n">
-        <v>3.408484</v>
-      </c>
-      <c r="L166" s="5" t="n">
-        <v>-1.946548</v>
+        <v>0.005183</v>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M166" t="inlineStr">
         <is>
@@ -15327,7 +15273,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Net and comprehensive loss - - (35,155)</t>
+          <t>Equity portion of Convertible Debentures 7 - 60,025 -</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
@@ -15362,10 +15308,12 @@
         </is>
       </c>
       <c r="K167" s="5" t="n">
-        <v>-0.357781</v>
-      </c>
-      <c r="L167" s="5" t="n">
-        <v>-0.322626</v>
+        <v>0.060025</v>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M167" t="inlineStr">
         <is>
@@ -15386,7 +15334,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2024 $ 4,725,998 $ 677,302 $ (83,423) $</t>
+          <t>Net and comprehensive loss - - (51,183)</t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
@@ -15421,10 +15369,10 @@
         </is>
       </c>
       <c r="K168" s="5" t="n">
-        <v>3.050703</v>
+        <v>-0.681709</v>
       </c>
       <c r="L168" s="5" t="n">
-        <v>-2.269174</v>
+        <v>-0.630526</v>
       </c>
       <c r="M168" t="inlineStr">
         <is>
@@ -15440,12 +15388,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Notes     Share Capital           Surplus            OCI             Deficit           Equity</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Stock-based compensation 8(d)</t>
+          <t>Balance December 31, 2023 $ 4,725,998 $ 677,302 $ (48,268) $</t>
         </is>
       </c>
       <c r="D169" t="inlineStr"/>
@@ -15474,16 +15422,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J169" s="5" t="n">
-        <v>0.05395</v>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K169" s="5" t="n">
-        <v>0.005183</v>
-      </c>
-      <c r="L169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.408484</v>
+      </c>
+      <c r="L169" s="5" t="n">
+        <v>-1.946548</v>
       </c>
       <c r="M169" t="inlineStr">
         <is>
@@ -15499,12 +15447,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Notes     Share Capital           Surplus            OCI             Deficit           Equity</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Debenture interest 7</t>
+          <t>Net and comprehensive loss - - (35,155)</t>
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
@@ -15539,12 +15487,10 @@
         </is>
       </c>
       <c r="K170" s="5" t="n">
-        <v>0.041708</v>
-      </c>
-      <c r="L170" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.357781</v>
+      </c>
+      <c r="L170" s="5" t="n">
+        <v>-0.322626</v>
       </c>
       <c r="M170" t="inlineStr">
         <is>
@@ -15560,12 +15506,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Notes     Share Capital           Surplus            OCI             Deficit           Equity</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Debenture accretion 7</t>
+          <t>Balance, December 31, 2024 $ 4,725,998 $ 677,302 $ (83,423) $</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
@@ -15600,12 +15546,10 @@
         </is>
       </c>
       <c r="K171" s="5" t="n">
-        <v>0.027017</v>
-      </c>
-      <c r="L171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.050703</v>
+      </c>
+      <c r="L171" s="5" t="n">
+        <v>-2.269174</v>
       </c>
       <c r="M171" t="inlineStr">
         <is>
@@ -15626,7 +15570,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Impairment 4</t>
+          <t>Stock-based compensation 8(d)</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
@@ -15655,13 +15599,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J172" s="5" t="n">
+        <v>0.05395</v>
       </c>
       <c r="K172" s="5" t="n">
-        <v>0.438393</v>
+        <v>0.005183</v>
       </c>
       <c r="L172" t="inlineStr">
         <is>
@@ -15682,12 +15624,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Other comprehensive income</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Foreign exchange translation adjustment</t>
+          <t>Debenture interest 7</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
@@ -15711,14 +15653,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I173" s="5" t="n">
-        <v>0.002934</v>
-      </c>
-      <c r="J173" s="5" t="n">
-        <v>-1.9e-05</v>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K173" s="5" t="n">
-        <v>-0.051183</v>
+        <v>0.041708</v>
       </c>
       <c r="L173" t="inlineStr">
         <is>
@@ -15739,12 +15685,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Notes    Share Capital          Surplus            OCI             Deficit            Equity</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>As at December 31, 2021 $ 4,725,998 $ 558,144 $ 2,934 $</t>
+          <t>Debenture accretion 7</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
@@ -15773,11 +15719,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J174" s="5" t="n">
-        <v>4.221423</v>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K174" s="5" t="n">
-        <v>-1.065653</v>
+        <v>0.027017</v>
       </c>
       <c r="L174" t="inlineStr">
         <is>
@@ -15798,12 +15746,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Notes    Share Capital          Surplus            OCI             Deficit            Equity</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Share-based compensation 8 (d) - 53,950 -</t>
+          <t>Impairment 4</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
@@ -15832,13 +15780,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J175" s="5" t="n">
-        <v>0.05395</v>
-      </c>
-      <c r="K175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K175" s="5" t="n">
+        <v>0.438393</v>
       </c>
       <c r="L175" t="inlineStr">
         <is>
@@ -15859,12 +15807,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Notes    Share Capital          Surplus            OCI             Deficit            Equity</t>
+          <t>Other comprehensive income</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Net and comprehensive loss - - (19)</t>
+          <t>Foreign exchange translation adjustment</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
@@ -15888,16 +15836,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I176" s="5" t="n">
+        <v>0.002934</v>
       </c>
       <c r="J176" s="5" t="n">
-        <v>-0.250388</v>
+        <v>-1.9e-05</v>
       </c>
       <c r="K176" s="5" t="n">
-        <v>-0.250369</v>
+        <v>-0.051183</v>
       </c>
       <c r="L176" t="inlineStr">
         <is>
@@ -15923,7 +15869,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Balance December 31, 2022 $ 4,725,998 $ 612,094 $ 2,915 $</t>
+          <t>As at December 31, 2021 $ 4,725,998 $ 558,144 $ 2,934 $</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
@@ -15953,10 +15899,10 @@
         </is>
       </c>
       <c r="J177" s="5" t="n">
-        <v>4.024985</v>
+        <v>4.221423</v>
       </c>
       <c r="K177" s="5" t="n">
-        <v>-1.316022</v>
+        <v>-1.065653</v>
       </c>
       <c r="L177" t="inlineStr">
         <is>
@@ -15982,7 +15928,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Share-based compensation 8 (d) - 5,183 -</t>
+          <t>Share-based compensation 8 (d) - 53,950 -</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
@@ -16012,7 +15958,7 @@
         </is>
       </c>
       <c r="J178" s="5" t="n">
-        <v>0.005183</v>
+        <v>0.05395</v>
       </c>
       <c r="K178" t="inlineStr">
         <is>
@@ -16043,7 +15989,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Equity portion of convertible note 7 - 60,025 -</t>
+          <t>Net and comprehensive loss - - (19)</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
@@ -16073,12 +16019,10 @@
         </is>
       </c>
       <c r="J179" s="5" t="n">
-        <v>0.060025</v>
-      </c>
-      <c r="K179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.250388</v>
+      </c>
+      <c r="K179" s="5" t="n">
+        <v>-0.250369</v>
       </c>
       <c r="L179" t="inlineStr">
         <is>
@@ -16104,7 +16048,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Net and comprehensive loss - - (51,183)</t>
+          <t>Balance December 31, 2022 $ 4,725,998 $ 612,094 $ 2,915 $</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
@@ -16134,10 +16078,10 @@
         </is>
       </c>
       <c r="J180" s="5" t="n">
-        <v>-0.681709</v>
+        <v>4.024985</v>
       </c>
       <c r="K180" s="5" t="n">
-        <v>-0.630526</v>
+        <v>-1.316022</v>
       </c>
       <c r="L180" t="inlineStr">
         <is>
@@ -16163,7 +16107,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2023 $ 4,725,998 $ 677,302 $ (48,268) $</t>
+          <t>Share-based compensation 8 (d) - 5,183 -</t>
         </is>
       </c>
       <c r="D181" t="inlineStr"/>
@@ -16193,10 +16137,12 @@
         </is>
       </c>
       <c r="J181" s="5" t="n">
-        <v>3.408484</v>
-      </c>
-      <c r="K181" s="5" t="n">
-        <v>-1.946548</v>
+        <v>0.005183</v>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
@@ -16217,19 +16163,15 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Notes    Share Capital          Surplus            OCI             Deficit            Equity</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>General and administrative 7 $</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Equity portion of convertible note 7 - 60,025 -</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr"/>
       <c r="E182" t="inlineStr">
         <is>
           <t>-</t>
@@ -16250,11 +16192,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I182" s="5" t="n">
-        <v>0.165417</v>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J182" s="5" t="n">
-        <v>0.237332</v>
+        <v>0.060025</v>
       </c>
       <c r="K182" t="inlineStr">
         <is>
@@ -16280,19 +16224,15 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Notes    Share Capital          Surplus            OCI             Deficit            Equity</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Unrealized (gain) loss on foreign exchange</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Net and comprehensive loss - - (51,183)</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr">
         <is>
           <t>-</t>
@@ -16313,16 +16253,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I183" s="5" t="n">
-        <v>0.078955</v>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J183" s="5" t="n">
-        <v>-0.040913</v>
-      </c>
-      <c r="K183" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.681709</v>
+      </c>
+      <c r="K183" s="5" t="n">
+        <v>-0.630526</v>
       </c>
       <c r="L183" t="inlineStr">
         <is>
@@ -16343,12 +16283,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Notes    Share Capital          Surplus            OCI             Deficit            Equity</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Stock-based compensation 6(d)</t>
+          <t>Balance, December 31, 2023 $ 4,725,998 $ 677,302 $ (48,268) $</t>
         </is>
       </c>
       <c r="D184" t="inlineStr"/>
@@ -16372,16 +16312,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I184" s="5" t="n">
-        <v>0.156667</v>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J184" s="5" t="n">
-        <v>0.05395</v>
-      </c>
-      <c r="K184" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.408484</v>
+      </c>
+      <c r="K184" s="5" t="n">
+        <v>-1.946548</v>
       </c>
       <c r="L184" t="inlineStr">
         <is>
@@ -16402,15 +16342,19 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Weighted average common shares:                         6</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Basic and diluted (post-consolidation)</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr"/>
+          <t>General and administrative 7 $</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E185" t="inlineStr">
         <is>
           <t>-</t>
@@ -16432,10 +16376,10 @@
         </is>
       </c>
       <c r="I185" s="5" t="n">
-        <v>28.603279</v>
+        <v>0.165417</v>
       </c>
       <c r="J185" s="5" t="n">
-        <v>29.648484</v>
+        <v>0.237332</v>
       </c>
       <c r="K185" t="inlineStr">
         <is>
@@ -16461,15 +16405,19 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Notes   Share Capital        Surplus          OCI           Deficit         Equity</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>As at December 31, 2020 $ 4,565,587 $ 211,888 $ - $</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr"/>
+          <t>Unrealized (gain) loss on foreign exchange</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E186" t="inlineStr">
         <is>
           <t>-</t>
@@ -16491,10 +16439,10 @@
         </is>
       </c>
       <c r="I186" s="5" t="n">
-        <v>4.112861</v>
+        <v>0.078955</v>
       </c>
       <c r="J186" s="5" t="n">
-        <v>-0.664614</v>
+        <v>-0.040913</v>
       </c>
       <c r="K186" t="inlineStr">
         <is>
@@ -16520,12 +16468,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Notes   Share Capital        Surplus          OCI           Deficit         Equity</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Issuance of common shares 6 350,000 - -</t>
+          <t>Stock-based compensation 6(d)</t>
         </is>
       </c>
       <c r="D187" t="inlineStr"/>
@@ -16550,12 +16498,10 @@
         </is>
       </c>
       <c r="I187" s="5" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="J187" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.156667</v>
+      </c>
+      <c r="J187" s="5" t="n">
+        <v>0.05395</v>
       </c>
       <c r="K187" t="inlineStr">
         <is>
@@ -16581,12 +16527,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Notes   Share Capital        Surplus          OCI           Deficit         Equity</t>
+          <t>Weighted average common shares:                         6</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Fair value of warrants 6 (189,589) 189,589 -</t>
+          <t>Basic and diluted (post-consolidation)</t>
         </is>
       </c>
       <c r="D188" t="inlineStr"/>
@@ -16610,15 +16556,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I188" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J188" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I188" s="5" t="n">
+        <v>28.603279</v>
+      </c>
+      <c r="J188" s="5" t="n">
+        <v>29.648484</v>
       </c>
       <c r="K188" t="inlineStr">
         <is>
@@ -16649,7 +16591,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Share-based compensation 6 - 156,667 -</t>
+          <t>As at December 31, 2020 $ 4,565,587 $ 211,888 $ - $</t>
         </is>
       </c>
       <c r="D189" t="inlineStr"/>
@@ -16674,12 +16616,10 @@
         </is>
       </c>
       <c r="I189" s="5" t="n">
-        <v>0.156667</v>
-      </c>
-      <c r="J189" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4.112861</v>
+      </c>
+      <c r="J189" s="5" t="n">
+        <v>-0.664614</v>
       </c>
       <c r="K189" t="inlineStr">
         <is>
@@ -16710,14 +16650,10 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Net and comprehensive loss - - 2,934</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Issuance of common shares 6 350,000 - -</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr">
         <is>
           <t>-</t>
@@ -16733,14 +16669,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H190" s="5" t="n">
-        <v>-0.398105</v>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I190" s="5" t="n">
-        <v>-0.398105</v>
-      </c>
-      <c r="J190" s="5" t="n">
-        <v>-0.401039</v>
+        <v>0.35</v>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K190" t="inlineStr">
         <is>
@@ -16771,7 +16711,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Balance December 31, 2021 $ 4,725,998 $ 558,144 $ 2,934 $</t>
+          <t>Fair value of warrants 6 (189,589) 189,589 -</t>
         </is>
       </c>
       <c r="D191" t="inlineStr"/>
@@ -16795,11 +16735,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I191" s="5" t="n">
-        <v>4.221423</v>
-      </c>
-      <c r="J191" s="5" t="n">
-        <v>-1.065653</v>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K191" t="inlineStr">
         <is>
@@ -16830,7 +16774,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Share-based compensation 6 - 53,950 -</t>
+          <t>Share-based compensation 6 - 156,667 -</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
@@ -16855,7 +16799,7 @@
         </is>
       </c>
       <c r="I192" s="5" t="n">
-        <v>0.05395</v>
+        <v>0.156667</v>
       </c>
       <c r="J192" t="inlineStr">
         <is>
@@ -16891,10 +16835,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Net and comprehensive loss - - (19)</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr"/>
+          <t>Net and comprehensive loss - - 2,934</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E193" t="inlineStr">
         <is>
           <t>-</t>
@@ -16910,16 +16858,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H193" s="5" t="n">
+        <v>-0.398105</v>
       </c>
       <c r="I193" s="5" t="n">
-        <v>-0.250388</v>
+        <v>-0.398105</v>
       </c>
       <c r="J193" s="5" t="n">
-        <v>-0.250369</v>
+        <v>-0.401039</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
@@ -16950,7 +16896,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2022 $ 4,725,998 $ 612,094 $ 2,915 $</t>
+          <t>Balance December 31, 2021 $ 4,725,998 $ 558,144 $ 2,934 $</t>
         </is>
       </c>
       <c r="D194" t="inlineStr"/>
@@ -16975,10 +16921,10 @@
         </is>
       </c>
       <c r="I194" s="5" t="n">
-        <v>4.024985</v>
+        <v>4.221423</v>
       </c>
       <c r="J194" s="5" t="n">
-        <v>-1.316022</v>
+        <v>-1.065653</v>
       </c>
       <c r="K194" t="inlineStr">
         <is>
@@ -17004,19 +16950,15 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Expenses                                                                                                    (Restated – Note 15)</t>
+          <t>Notes   Share Capital        Surplus          OCI           Deficit         Equity</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>General and administrative 8 $</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Share-based compensation 6 - 53,950 -</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
@@ -17032,11 +16974,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H195" s="5" t="n">
-        <v>0.315381</v>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I195" s="5" t="n">
-        <v>0.165417</v>
+        <v>0.05395</v>
       </c>
       <c r="J195" t="inlineStr">
         <is>
@@ -17067,19 +17011,15 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Expenses                                                                                                    (Restated – Note 15)</t>
+          <t>Notes   Share Capital        Surplus          OCI           Deficit         Equity</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Realized foreign exchange loss</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Net and comprehensive loss - - (19)</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr">
         <is>
           <t>-</t>
@@ -17095,18 +17035,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H196" s="5" t="n">
-        <v>0.025575</v>
-      </c>
-      <c r="I196" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J196" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I196" s="5" t="n">
+        <v>-0.250388</v>
+      </c>
+      <c r="J196" s="5" t="n">
+        <v>-0.250369</v>
       </c>
       <c r="K196" t="inlineStr">
         <is>
@@ -17132,19 +17070,15 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Expenses                                                                                                    (Restated – Note 15)</t>
+          <t>Notes   Share Capital        Surplus          OCI           Deficit         Equity</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Unrealized loss on foreign exchange</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Balance, December 31, 2022 $ 4,725,998 $ 612,094 $ 2,915 $</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr">
         <is>
           <t>-</t>
@@ -17166,12 +17100,10 @@
         </is>
       </c>
       <c r="I197" s="5" t="n">
-        <v>0.078955</v>
-      </c>
-      <c r="J197" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4.024985</v>
+      </c>
+      <c r="J197" s="5" t="n">
+        <v>-1.316022</v>
       </c>
       <c r="K197" t="inlineStr">
         <is>
@@ -17202,10 +17134,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Stock-based compensation 7(d)</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr"/>
+          <t>General and administrative 8 $</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E198" t="inlineStr">
         <is>
           <t>-</t>
@@ -17222,10 +17158,10 @@
         </is>
       </c>
       <c r="H198" s="5" t="n">
-        <v>0.09800499999999999</v>
+        <v>0.315381</v>
       </c>
       <c r="I198" s="5" t="n">
-        <v>0.156667</v>
+        <v>0.165417</v>
       </c>
       <c r="J198" t="inlineStr">
         <is>
@@ -17261,10 +17197,14 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Expenses                                                                                                    (Restated – Note 15) total</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr"/>
+          <t>Realized foreign exchange loss</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr">
         <is>
           <t>-</t>
@@ -17281,10 +17221,12 @@
         </is>
       </c>
       <c r="H199" s="5" t="n">
-        <v>0.438961</v>
-      </c>
-      <c r="I199" s="5" t="n">
-        <v>0.401039</v>
+        <v>0.025575</v>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
@@ -17320,12 +17262,12 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Net loss</t>
+          <t>Unrealized loss on foreign exchange</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -17343,11 +17285,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H200" s="5" t="n">
-        <v>-0.438961</v>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I200" s="5" t="n">
-        <v>-0.401039</v>
+        <v>0.078955</v>
       </c>
       <c r="J200" t="inlineStr">
         <is>
@@ -17378,12 +17322,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Weighted average common shares:                         7</t>
+          <t>Expenses                                                                                                    (Restated – Note 15)</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Basic and diluted (post-consolidation)</t>
+          <t>Stock-based compensation 7(d)</t>
         </is>
       </c>
       <c r="D201" t="inlineStr"/>
@@ -17403,10 +17347,10 @@
         </is>
       </c>
       <c r="H201" s="5" t="n">
-        <v>7.363015</v>
+        <v>0.09800499999999999</v>
       </c>
       <c r="I201" s="5" t="n">
-        <v>28.603279</v>
+        <v>0.156667</v>
       </c>
       <c r="J201" t="inlineStr">
         <is>
@@ -17437,12 +17381,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Notes   Share Capital        Surplus          OCI           Deficit         Equity</t>
+          <t>Expenses                                                                                                    (Restated – Note 15)</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>As at December 31, 2019 $ 640,782 $ 106,410 $ - $</t>
+          <t>Expenses                                                                                                    (Restated – Note 15) total</t>
         </is>
       </c>
       <c r="D202" t="inlineStr"/>
@@ -17462,10 +17406,10 @@
         </is>
       </c>
       <c r="H202" s="5" t="n">
-        <v>0.521539</v>
+        <v>0.438961</v>
       </c>
       <c r="I202" s="5" t="n">
-        <v>-0.225653</v>
+        <v>0.401039</v>
       </c>
       <c r="J202" t="inlineStr">
         <is>
@@ -17496,15 +17440,19 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Notes   Share Capital        Surplus          OCI           Deficit         Equity</t>
+          <t>Expenses                                                                                                    (Restated – Note 15)</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Issuance of common shares 3,943,250 - -</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr"/>
+          <t>Net loss</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
           <t>-</t>
@@ -17521,12 +17469,10 @@
         </is>
       </c>
       <c r="H203" s="5" t="n">
-        <v>3.94325</v>
-      </c>
-      <c r="I203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.438961</v>
+      </c>
+      <c r="I203" s="5" t="n">
+        <v>-0.401039</v>
       </c>
       <c r="J203" t="inlineStr">
         <is>
@@ -17557,12 +17503,12 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Notes   Share Capital        Surplus          OCI           Deficit         Equity</t>
+          <t>Weighted average common shares:                         7</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Share issue costs (10,972) - -</t>
+          <t>Basic and diluted (post-consolidation)</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
@@ -17582,12 +17528,10 @@
         </is>
       </c>
       <c r="H204" s="5" t="n">
-        <v>-0.010972</v>
-      </c>
-      <c r="I204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>7.363015</v>
+      </c>
+      <c r="I204" s="5" t="n">
+        <v>28.603279</v>
       </c>
       <c r="J204" t="inlineStr">
         <is>
@@ -17623,7 +17567,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Fair value of broker warrants (7,473) 7,473 -</t>
+          <t>As at December 31, 2019 $ 640,782 $ 106,410 $ - $</t>
         </is>
       </c>
       <c r="D205" t="inlineStr"/>
@@ -17642,15 +17586,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I205" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H205" s="5" t="n">
+        <v>0.521539</v>
+      </c>
+      <c r="I205" s="5" t="n">
+        <v>-0.225653</v>
       </c>
       <c r="J205" t="inlineStr">
         <is>
@@ -17686,7 +17626,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Fair value of stock options - 98,005 -</t>
+          <t>Issuance of common shares 3,943,250 - -</t>
         </is>
       </c>
       <c r="D206" t="inlineStr"/>
@@ -17706,7 +17646,7 @@
         </is>
       </c>
       <c r="H206" s="5" t="n">
-        <v>0.09800499999999999</v>
+        <v>3.94325</v>
       </c>
       <c r="I206" t="inlineStr">
         <is>
@@ -17747,14 +17687,10 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Net loss - - -</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Share issue costs (10,972) - -</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr"/>
       <c r="E207" t="inlineStr">
         <is>
           <t>-</t>
@@ -17771,10 +17707,12 @@
         </is>
       </c>
       <c r="H207" s="5" t="n">
-        <v>-0.438961</v>
-      </c>
-      <c r="I207" s="5" t="n">
-        <v>-0.438961</v>
+        <v>-0.010972</v>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
@@ -17810,7 +17748,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Balance December</t>
+          <t>Fair value of broker warrants (7,473) 7,473 -</t>
         </is>
       </c>
       <c r="D208" t="inlineStr"/>
@@ -17829,11 +17767,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H208" s="5" t="n">
-        <v>0.00202</v>
-      </c>
-      <c r="I208" s="5" t="n">
-        <v>3.1e-05</v>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
@@ -17869,7 +17811,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>(Restated – Note 15) $ 4,565,587 $ 211,888 $ - $</t>
+          <t>Fair value of stock options - 98,005 -</t>
         </is>
       </c>
       <c r="D209" t="inlineStr"/>
@@ -17889,10 +17831,12 @@
         </is>
       </c>
       <c r="H209" s="5" t="n">
-        <v>4.112861</v>
-      </c>
-      <c r="I209" s="5" t="n">
-        <v>-0.664614</v>
+        <v>0.09800499999999999</v>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
@@ -17928,10 +17872,14 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Issuance of common shares 7 350,000 - -</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr"/>
+          <t>Net loss - - -</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E210" t="inlineStr">
         <is>
           <t>-</t>
@@ -17948,12 +17896,10 @@
         </is>
       </c>
       <c r="H210" s="5" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="I210" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.438961</v>
+      </c>
+      <c r="I210" s="5" t="n">
+        <v>-0.438961</v>
       </c>
       <c r="J210" t="inlineStr">
         <is>
@@ -17989,7 +17935,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Fair value of warrants (189,589) 189,589 -</t>
+          <t>Balance December</t>
         </is>
       </c>
       <c r="D211" t="inlineStr"/>
@@ -18008,15 +17954,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H211" s="5" t="n">
+        <v>0.00202</v>
+      </c>
+      <c r="I211" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="J211" t="inlineStr">
         <is>
@@ -18052,7 +17994,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Share-based compensation - 156,667 -</t>
+          <t>(Restated – Note 15) $ 4,565,587 $ 211,888 $ - $</t>
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
@@ -18072,12 +18014,10 @@
         </is>
       </c>
       <c r="H212" s="5" t="n">
-        <v>0.156667</v>
-      </c>
-      <c r="I212" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4.112861</v>
+      </c>
+      <c r="I212" s="5" t="n">
+        <v>-0.664614</v>
       </c>
       <c r="J212" t="inlineStr">
         <is>
@@ -18113,7 +18053,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2021 $ 4,725,998 $ 558,144 $ 2,934 $</t>
+          <t>Issuance of common shares 7 350,000 - -</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
@@ -18133,10 +18073,12 @@
         </is>
       </c>
       <c r="H213" s="5" t="n">
-        <v>4.221423</v>
-      </c>
-      <c r="I213" s="5" t="n">
-        <v>-1.065653</v>
+        <v>0.35</v>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
@@ -18167,19 +18109,15 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Notes   Share Capital        Surplus          OCI           Deficit         Equity</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>General and administrative 8 $</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Fair value of warrants (189,589) 189,589 -</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr"/>
       <c r="E214" t="inlineStr">
         <is>
           <t>-</t>
@@ -18190,11 +18128,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G214" s="5" t="n">
-        <v>0.057333</v>
-      </c>
-      <c r="H214" s="5" t="n">
-        <v>0.315381</v>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
@@ -18230,12 +18172,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Notes   Share Capital        Surplus          OCI           Deficit         Equity</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Share-based compensation 7(d)</t>
+          <t>Share-based compensation - 156,667 -</t>
         </is>
       </c>
       <c r="D215" t="inlineStr"/>
@@ -18255,7 +18197,7 @@
         </is>
       </c>
       <c r="H215" s="5" t="n">
-        <v>0.294015</v>
+        <v>0.156667</v>
       </c>
       <c r="I215" t="inlineStr">
         <is>
@@ -18291,19 +18233,15 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Notes   Share Capital        Surplus          OCI           Deficit         Equity</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Realized foreign exchange loss</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Balance, December 31, 2021 $ 4,725,998 $ 558,144 $ 2,934 $</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr"/>
       <c r="E216" t="inlineStr">
         <is>
           <t>-</t>
@@ -18320,12 +18258,10 @@
         </is>
       </c>
       <c r="H216" s="5" t="n">
-        <v>0.025575</v>
-      </c>
-      <c r="I216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4.221423</v>
+      </c>
+      <c r="I216" s="5" t="n">
+        <v>-1.065653</v>
       </c>
       <c r="J216" t="inlineStr">
         <is>
@@ -18361,16 +18297,18 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss $</t>
+          <t>General and administrative 8 $</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E217" s="5" t="n">
-        <v>-0.16832</v>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18378,10 +18316,10 @@
         </is>
       </c>
       <c r="G217" s="5" t="n">
-        <v>-0.057333</v>
+        <v>0.057333</v>
       </c>
       <c r="H217" s="5" t="n">
-        <v>-0.634971</v>
+        <v>0.315381</v>
       </c>
       <c r="I217" t="inlineStr">
         <is>
@@ -18417,12 +18355,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Weighted average common shares:            7</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Basic and diluted (post-consolidation)</t>
+          <t>Share-based compensation 7(d)</t>
         </is>
       </c>
       <c r="D218" t="inlineStr"/>
@@ -18436,11 +18374,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G218" s="5" t="n">
-        <v>0.666667</v>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H218" s="5" t="n">
-        <v>7.363015</v>
+        <v>0.294015</v>
       </c>
       <c r="I218" t="inlineStr">
         <is>
@@ -18476,15 +18416,19 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Notes     Share Capital          Surplus             Deficit            Equity</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>As at December 31, 2018 $ 640,782 $ 106,410 $</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr"/>
+          <t>Realized foreign exchange loss</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E219" t="inlineStr">
         <is>
           <t>-</t>
@@ -18495,11 +18439,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G219" s="5" t="n">
-        <v>0.5788720000000001</v>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H219" s="5" t="n">
-        <v>-0.16832</v>
+        <v>0.025575</v>
       </c>
       <c r="I219" t="inlineStr">
         <is>
@@ -18535,12 +18481,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Notes     Share Capital          Surplus             Deficit            Equity</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Net loss - -</t>
+          <t>Net loss and comprehensive loss $</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -18548,10 +18494,8 @@
           <t>NetIncome</t>
         </is>
       </c>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E220" s="5" t="n">
+        <v>-0.16832</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18562,7 +18506,7 @@
         <v>-0.057333</v>
       </c>
       <c r="H220" s="5" t="n">
-        <v>-0.057333</v>
+        <v>-0.634971</v>
       </c>
       <c r="I220" t="inlineStr">
         <is>
@@ -18598,12 +18542,12 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Notes     Share Capital          Surplus             Deficit            Equity</t>
+          <t>Weighted average common shares:            7</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Balance December 31, 2019 $ 640,782 $ 106,410 $</t>
+          <t>Basic and diluted (post-consolidation)</t>
         </is>
       </c>
       <c r="D221" t="inlineStr"/>
@@ -18618,10 +18562,10 @@
         </is>
       </c>
       <c r="G221" s="5" t="n">
-        <v>0.521539</v>
+        <v>0.666667</v>
       </c>
       <c r="H221" s="5" t="n">
-        <v>-0.225653</v>
+        <v>7.363015</v>
       </c>
       <c r="I221" t="inlineStr">
         <is>
@@ -18662,7 +18606,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Issuance of common shares 3,943,250 -</t>
+          <t>As at December 31, 2018 $ 640,782 $ 106,410 $</t>
         </is>
       </c>
       <c r="D222" t="inlineStr"/>
@@ -18677,12 +18621,10 @@
         </is>
       </c>
       <c r="G222" s="5" t="n">
-        <v>3.94325</v>
-      </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.5788720000000001</v>
+      </c>
+      <c r="H222" s="5" t="n">
+        <v>-0.16832</v>
       </c>
       <c r="I222" t="inlineStr">
         <is>
@@ -18723,10 +18665,14 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Share issue costs 7 (10,972) -</t>
-        </is>
-      </c>
-      <c r="D223" t="inlineStr"/>
+          <t>Net loss - -</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E223" t="inlineStr">
         <is>
           <t>-</t>
@@ -18738,12 +18684,10 @@
         </is>
       </c>
       <c r="G223" s="5" t="n">
-        <v>-0.010972</v>
-      </c>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.057333</v>
+      </c>
+      <c r="H223" s="5" t="n">
+        <v>-0.057333</v>
       </c>
       <c r="I223" t="inlineStr">
         <is>
@@ -18784,7 +18728,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Fair value of broker warrants 7 (7,473) 7,473</t>
+          <t>Balance December 31, 2019 $ 640,782 $ 106,410 $</t>
         </is>
       </c>
       <c r="D224" t="inlineStr"/>
@@ -18798,15 +18742,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G224" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G224" s="5" t="n">
+        <v>0.521539</v>
+      </c>
+      <c r="H224" s="5" t="n">
+        <v>-0.225653</v>
       </c>
       <c r="I224" t="inlineStr">
         <is>
@@ -18847,7 +18787,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Fair value of stock options 7 - 294,015</t>
+          <t>Issuance of common shares 3,943,250 -</t>
         </is>
       </c>
       <c r="D225" t="inlineStr"/>
@@ -18862,7 +18802,7 @@
         </is>
       </c>
       <c r="G225" s="5" t="n">
-        <v>0.294015</v>
+        <v>3.94325</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
@@ -18908,7 +18848,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2020 $ 4,565,587 $ 407,898 $</t>
+          <t>Share issue costs 7 (10,972) -</t>
         </is>
       </c>
       <c r="D226" t="inlineStr"/>
@@ -18923,10 +18863,12 @@
         </is>
       </c>
       <c r="G226" s="5" t="n">
-        <v>4.112861</v>
-      </c>
-      <c r="H226" s="5" t="n">
-        <v>-0.8606239999999999</v>
+        <v>-0.010972</v>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
@@ -18962,21 +18904,19 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Notes     Share Capital          Surplus             Deficit            Equity</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Professional fees $</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E227" s="5" t="n">
-        <v>0.009476999999999999</v>
+          <t>Fair value of broker warrants 7 (7,473) 7,473</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr"/>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19027,31 +18967,27 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Notes     Share Capital          Surplus             Deficit            Equity</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>General and administrative</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
-      <c r="E228" s="5" t="n">
-        <v>0.061033</v>
+          <t>Fair value of stock options 7 - 294,015</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr"/>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G228" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G228" s="5" t="n">
+        <v>0.294015</v>
       </c>
       <c r="H228" t="inlineStr">
         <is>
@@ -19092,32 +19028,30 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Notes     Share Capital          Surplus             Deficit            Equity</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Stock-based compensation (Note 4)</t>
+          <t>Balance, December 31, 2020 $ 4,565,587 $ 407,898 $</t>
         </is>
       </c>
       <c r="D229" t="inlineStr"/>
-      <c r="E229" s="5" t="n">
-        <v>0.09780999999999999</v>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G229" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H229" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G229" s="5" t="n">
+        <v>4.112861</v>
+      </c>
+      <c r="H229" s="5" t="n">
+        <v>-0.8606239999999999</v>
       </c>
       <c r="I229" t="inlineStr">
         <is>
@@ -19158,12 +19092,16 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Loss per share: (Note</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr"/>
+          <t>Professional fees $</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E230" s="5" t="n">
-        <v>6e-06</v>
+        <v>0.009476999999999999</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19219,12 +19157,16 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Basic and diluted</t>
-        </is>
-      </c>
-      <c r="D231" t="inlineStr"/>
+          <t>General and administrative</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E231" s="5" t="n">
-        <v>-1.8e-07</v>
+        <v>0.061033</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19280,12 +19222,12 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Weighted average common shares: (Note</t>
+          <t>Stock-based compensation (Note 4)</t>
         </is>
       </c>
       <c r="D232" t="inlineStr"/>
       <c r="E232" s="5" t="n">
-        <v>6e-06</v>
+        <v>0.09780999999999999</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19336,19 +19278,17 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>($)        Surplus                 ($)                ($)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>At incorporation December 14, 2017 - - -</t>
+          <t>Loss per share: (Note</t>
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
-      <c r="E233" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E233" s="5" t="n">
+        <v>6e-06</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19399,17 +19339,17 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>($)        Surplus                 ($)                ($)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Share issuance (Note 6) 700,000 - -</t>
+          <t>Basic and diluted</t>
         </is>
       </c>
       <c r="D234" t="inlineStr"/>
       <c r="E234" s="5" t="n">
-        <v>0.7</v>
+        <v>-1.8e-07</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19460,17 +19400,17 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>($)        Surplus                 ($)                ($)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Share issue cost (59,218) 8,600 -</t>
+          <t>Weighted average common shares: (Note</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
       <c r="E235" s="5" t="n">
-        <v>-0.050618</v>
+        <v>6e-06</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19526,12 +19466,14 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Director and officer options granted - 97,810 -</t>
+          <t>At incorporation December 14, 2017 - - -</t>
         </is>
       </c>
       <c r="D236" t="inlineStr"/>
-      <c r="E236" s="5" t="n">
-        <v>0.09780999999999999</v>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19587,12 +19529,12 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Net loss - - (168,320)</t>
+          <t>Share issuance (Note 6) 700,000 - -</t>
         </is>
       </c>
       <c r="D237" t="inlineStr"/>
       <c r="E237" s="5" t="n">
-        <v>-0.16832</v>
+        <v>0.7</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19648,49 +19590,232 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>As at December 31, 2018 640,782 106,410 (168,320)</t>
+          <t>Share issue cost (59,218) 8,600 -</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
       <c r="E238" s="5" t="n">
+        <v>-0.050618</v>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>($)        Surplus                 ($)                ($)</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Director and officer options granted - 97,810 -</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr"/>
+      <c r="E239" s="5" t="n">
+        <v>0.09780999999999999</v>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>($)        Surplus                 ($)                ($)</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Net loss - - (168,320)</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr"/>
+      <c r="E240" s="5" t="n">
+        <v>-0.16832</v>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>($)        Surplus                 ($)                ($)</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>As at December 31, 2018 640,782 106,410 (168,320)</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr"/>
+      <c r="E241" s="5" t="n">
         <v>-0.5788720000000001</v>
       </c>
-      <c r="F238" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G238" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H238" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I238" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J238" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K238" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L238" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M238" t="inlineStr">
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr">
         <is>
           <t>-</t>
         </is>
